--- a/data/trans_dic/P3A$pareja-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,66; 60,23</t>
+          <t>45,34; 59,86</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,96; 31,92</t>
+          <t>22,8; 31,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,24; 44,3</t>
+          <t>36,72; 44,94</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,85; 56,58</t>
+          <t>44,77; 55,62</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,47; 34,4</t>
+          <t>27,26; 34,52</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36,96; 43,87</t>
+          <t>37,42; 43,93</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,65; 49,28</t>
+          <t>38,34; 49,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,74; 34,33</t>
+          <t>25,76; 34,1</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32,91; 39,64</t>
+          <t>33,09; 39,55</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,22; 57,51</t>
+          <t>43,64; 57,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,33; 20,29</t>
+          <t>9,69; 20,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,54; 35,02</t>
+          <t>20,77; 34,69</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,37; 35,87</t>
+          <t>24,91; 35,67</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,47; 24,61</t>
+          <t>10,16; 25,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,26; 27,72</t>
+          <t>15,8; 28,0</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>43,8; 55,28</t>
+          <t>44,15; 55,12</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>33,72; 43,42</t>
+          <t>34,2; 43,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,57; 48,1</t>
+          <t>40,88; 48,23</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,13; 46,72</t>
+          <t>37,32; 46,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,83; 25,44</t>
+          <t>9,47; 25,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>17,54; 34,01</t>
+          <t>18,59; 34,04</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>18,58; 57,08</t>
+          <t>19,01; 57,01</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,87</t>
+          <t>5,08; 8,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,45; 31,07</t>
+          <t>16,29; 31,17</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34,93; 49,08</t>
+          <t>34,48; 49,17</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,91; 22,55</t>
+          <t>16,55; 22,72</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28,08; 34,81</t>
+          <t>28,13; 34,76</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que la pareja de la persona entrevistada se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente la pareja de la persona entrevistada se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>142214; 187585</t>
+          <t>141215; 186432</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66513; 92453</t>
+          <t>66039; 91371</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>217833; 266280</t>
+          <t>220689; 270095</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>232514; 293324</t>
+          <t>232091; 288315</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>141479; 177131</t>
+          <t>140362; 177746</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>381981; 453354</t>
+          <t>386690; 453908</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>121899; 155427</t>
+          <t>120941; 155509</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89549; 119419</t>
+          <t>89616; 118639</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>218299; 262931</t>
+          <t>219482; 262307</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>135082; 179763</t>
+          <t>136399; 180360</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>44401; 96540</t>
+          <t>46081; 96803</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>161928; 276055</t>
+          <t>163713; 273440</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>43443; 63944</t>
+          <t>44413; 63585</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24514; 63695</t>
+          <t>26280; 65513</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66683; 121170</t>
+          <t>69041; 122380</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>118095; 149061</t>
+          <t>119047; 148619</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>86667; 111604</t>
+          <t>87914; 112158</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>213664; 253333</t>
+          <t>215305; 254023</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>238052; 291643</t>
+          <t>232972; 290632</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>83453; 216081</t>
+          <t>80451; 214781</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>258445; 501135</t>
+          <t>273859; 501525</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>172551; 530126</t>
+          <t>176532; 529436</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>35904; 56513</t>
+          <t>36457; 57888</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>270859; 511625</t>
+          <t>268264; 513137</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1208113; 1697451</t>
+          <t>1192592; 1700703</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>627449; 836915</t>
+          <t>614292; 843229</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2013590; 2495759</t>
+          <t>2016671; 2492035</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$pareja-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$pareja-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>56,3%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,72%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>45,34; 59,86</t>
+          <t>50,22; 62,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>22,8; 31,55</t>
+          <t>21,31; 28,85</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36,72; 44,94</t>
+          <t>37,0; 44,57</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>44,77; 55,62</t>
+          <t>46,95; 57,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,26; 34,52</t>
+          <t>27,71; 35,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37,42; 43,93</t>
+          <t>38,2; 44,95</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>30,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>36,57%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>38,34; 49,3</t>
+          <t>38,21; 49,07</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>25,76; 34,1</t>
+          <t>26,48; 34,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>33,09; 39,55</t>
+          <t>33,02; 39,53</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>19,66%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>34,2%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>43,64; 57,7</t>
+          <t>43,94; 58,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,69; 20,35</t>
+          <t>16,45; 23,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,77; 34,69</t>
+          <t>30,42; 37,99</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>26,66%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>24,91; 35,67</t>
+          <t>25,37; 35,74</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 25,32</t>
+          <t>19,79; 27,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15,8; 28,0</t>
+          <t>23,2; 30,03</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>44,15; 55,12</t>
+          <t>45,02; 55,59</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>34,2; 43,63</t>
+          <t>33,46; 42,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40,88; 48,23</t>
+          <t>40,97; 47,92</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>37,32; 46,55</t>
+          <t>39,53; 47,86</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,47; 25,29</t>
+          <t>21,14; 26,46</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18,59; 34,04</t>
+          <t>31,11; 36,15</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>40,89%</t>
+          <t>55,07%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>30,21%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>19,01; 57,01</t>
+          <t>51,42; 58,9</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 8,07</t>
+          <t>4,97; 7,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,29; 31,17</t>
+          <t>28,04; 32,6</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>34,48; 49,17</t>
+          <t>47,17; 50,86</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16,55; 22,72</t>
+          <t>21,06; 23,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>28,13; 34,76</t>
+          <t>34,2; 36,53</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>165973</t>
+          <t>179523</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78290</t>
+          <t>79042</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>244263</t>
+          <t>258565</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>141215; 186432</t>
+          <t>160137; 197800</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>66039; 91371</t>
+          <t>67346; 91181</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>220689; 270095</t>
+          <t>234943; 282990</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>261595</t>
+          <t>278156</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>158596</t>
+          <t>171614</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>420191</t>
+          <t>449770</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>232091; 288315</t>
+          <t>249120; 305957</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>140362; 177746</t>
+          <t>151425; 192840</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>386690; 453908</t>
+          <t>411415; 484185</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>137457</t>
+          <t>136811</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>103627</t>
+          <t>108366</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>241084</t>
+          <t>245177</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>120941; 155509</t>
+          <t>120503; 154760</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>89616; 118639</t>
+          <t>94040; 121861</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>219482; 262307</t>
+          <t>221426; 265050</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>159071</t>
+          <t>189003</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>73945</t>
+          <t>82960</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>233015</t>
+          <t>271963</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>136399; 180360</t>
+          <t>163947; 217035</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>46081; 96803</t>
+          <t>69427; 97766</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>163713; 273440</t>
+          <t>241845; 302030</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>53501</t>
+          <t>62068</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>49536</t>
+          <t>53678</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>103037</t>
+          <t>115745</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>44413; 63585</t>
+          <t>52060; 73327</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>26280; 65513</t>
+          <t>45310; 62552</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>69041; 122380</t>
+          <t>100723; 130361</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>134109</t>
+          <t>137188</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>98934</t>
+          <t>100402</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>233044</t>
+          <t>237590</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>119047; 148619</t>
+          <t>121877; 150497</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>87914; 112158</t>
+          <t>88256; 112829</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>215305; 254023</t>
+          <t>218992; 256090</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>263493</t>
+          <t>315838</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>157019</t>
+          <t>182509</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>420512</t>
+          <t>498346</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>232972; 290632</t>
+          <t>284496; 344410</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>80451; 214781</t>
+          <t>163186; 204279</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>273859; 501525</t>
+          <t>464147; 539259</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>379752</t>
+          <t>439532</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>45823</t>
+          <t>52769</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>425575</t>
+          <t>492300</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>176532; 529436</t>
+          <t>410399; 470098</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>36457; 57888</t>
+          <t>41314; 66140</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>268264; 513137</t>
+          <t>456819; 531208</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>1554951</t>
+          <t>1738118</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>765770</t>
+          <t>831338</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2320721</t>
+          <t>2569457</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>1192592; 1700703</t>
+          <t>1665820; 1796052</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>614292; 843229</t>
+          <t>786819; 873757</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2016671; 2492035</t>
+          <t>2485627; 2654563</t>
         </is>
       </c>
     </row>
